--- a/field-guide/AI_Lab_Test_Log.xlsx
+++ b/field-guide/AI_Lab_Test_Log.xlsx
@@ -659,13 +659,13 @@
     <from>
       <col>6</col>
       <colOff>54430</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>43543</rowOff>
     </from>
     <to>
       <col>10</col>
       <colOff>529329</colOff>
-      <row>29</row>
+      <row>30</row>
       <rowOff>4103914</rowOff>
     </to>
     <pic>
@@ -1002,7 +1002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.6"/>
   <cols>
     <col width="21.4609375" customWidth="1" min="3" max="3"/>
@@ -2375,9 +2375,62 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="300" customHeight="1"/>
-    <row r="30" ht="332.15" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+    <row r="29" ht="29.15" customHeight="1">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Edge</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>Open WebUI chat</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>ai-lab-b:8080</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>answer in one sentence: why do cats purr?</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Measured</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Valid</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>A/B test of Open WebUI Task features. BASELINE (Title+FollowUp+Tags ON, all on qwen3:8b): 6 runs, thinking steady 11-13s, total median ~58s, overhead 18-86s and highly variable. FEATURES OFF: 8 runs, thinking still ~11s, total median ~13s, overhead collapsed to ~2s and variance gone. CONFIRMS the ~27-46s overhead was Title/Tags/FollowUp background calls each running full qwen3:8b. Fix chosen: leave the three OFF. Alt (untested): point Task Model at a small model to keep features + speed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="332.15" customHeight="1"/>
+    <row r="31" ht="332.15" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Conclusions After Tests 1–13
 Tests 1–13 established that the AI Lab stack can successfully provide both local and remote inference, while also revealing an unresolved intermittent remote-access reliability issue.. Open WebUI is listening on all network interfaces (0.0.0.0:8080), Ollama successfully loads and runs qwen3:8b, and the complete iPhone → Tailscale → Open WebUI → Ollama → qwen3:8b path successfully completed multiple queries. The Tailscale network connection between Lab PC 2 and the iPhone was independently verified with Tailscale ping. Windows identifies the Tailscale interface as Private, and the Windows Firewall rule allowing inbound TCP port 8080 is correctly configured.
@@ -2388,8 +2441,9 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="340" customHeight="1">
-      <c r="B32" s="8" t="inlineStr">
+    <row r="32" ht="340" customHeight="1"/>
+    <row r="33" ht="340" customHeight="1">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>Conclusions After Tests 14–20 (July 7–10)
 CONNECTIVITY — SOLVED. SleepStudy confirmed the Beelink entered Modern Standby a median of 17 s after display sleep, and across 77 sessions (122.6 h) was never woken by network traffic. The fix (powercfg: standby-timeout-ac 0, monitor-timeout-ac 10, July 7) removed the transition. Remote access then survived 6 h 02 m (Test 16) and ~6.5 h (Test 17a) of untouched idle — the exact scenario that failed at 4 h in Test 14. MagicDNS name access works from iPhone-on-cellular and from the recovered HP desktop (Tests 19, 17b).
@@ -2406,8 +2460,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B32:F32"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B33:F33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/field-guide/AI_Lab_Test_Log.xlsx
+++ b/field-guide/AI_Lab_Test_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e6708a7502f50cfc/Tony1/AI-Lab/Portal/field-guide/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_82C492D49402BEC24B5B26F6D884A707973BE388" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C54927CB-E536-4439-BB96-6308914AF646}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_82C492D49402BEC24B5B26F6D884A707973BE388" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EDA8AB4-AA6A-4DFF-B261-AABBE0915E5F}"/>
   <bookViews>
-    <workbookView xWindow="6086" yWindow="1757" windowWidth="26014" windowHeight="12669" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6086" yWindow="1757" windowWidth="10371" windowHeight="7089" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI_Lab_Test_Log" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="120">
   <si>
     <t>Test</t>
   </si>
@@ -367,6 +367,33 @@
   </si>
   <si>
     <t>RAG-path timing bench: paired A/B trials (RAG-attached vs plain), N=15/condition, 30/30 scored, 0 errors. Median overhead (wall clock minus Ollama's own total_duration): 11.7s (RAG) vs 2.3s (plain) -- ~9.4s attributable to Open WebUI's own RAG pipeline (retrieval/chunk assembly/injection), not model inference or embedding (embedding call ~0.04s median). Closes a meaningful chunk of Test 22's unresolved wall-clock gap. Confound flagged: RAG generation was shorter (30.7s) than plain (41.2s) since the plain condition can't answer the reused question and hedges at length -- isolated overhead_s is the reliable metric here, not raw wall clock. Mid-run catch: first execution attempt found the original #RAG Test text-prefix design does nothing over the raw API (frontend-only syntax); fixed via the files field, spec bumped to v3. Full detail: test-logs/Test23-log-entry.md.</t>
+  </si>
+  <si>
+    <t>Lab PC 2 + HP Desktop</t>
+  </si>
+  <si>
+    <t>Open WebUI (browser) + capture_proxy.py</t>
+  </si>
+  <si>
+    <t>Timer diagnostic</t>
+  </si>
+  <si>
+    <t>qwen3:8b, plain query, no RAG</t>
+  </si>
+  <si>
+    <t>why do cats purr? (standard prompt), 10+ rounds across 2 machines</t>
+  </si>
+  <si>
+    <t>Displayed: &lt;1s (bug)</t>
+  </si>
+  <si>
+    <t>20-49s real (stopwatch + Ollama total_duration agree within 1-3s)</t>
+  </si>
+  <si>
+    <t>Upstream Open WebUI timer bug confirmed</t>
+  </si>
+  <si>
+    <t>Open WebUI's on-screen 'Thought for Xs' timer showed &lt;1s on every round of a plain (non-RAG) 'why do cats purr?' query, across 10+ rounds on two separate machines (browser on Lab PC 2, then browser on the HP desktop over the network -- ruling out resource contention). Real latency agreed two independent ways: stopwatch and Ollama's own total_duration (via capture_proxy.py, same port-swap rig as Test 23) matched within 1-3s every round, 20-49s per round. Root cause confirmed from a persisted chat record (GET /api/v1/chats/{chat_id}): the same message held both the broken duration:0 (started_at/ended_at 0.19s apart, int-truncated) and Ollama's real usage.total_duration=21.80s side by side. Frontend (bundled DBZsSbCZ.js) confirmed innocent -- just renders the given duration int. Bug located in backend open_webui/utils/middleware.py (~2969-2994, duplicated ~4306-4372) timestamp stamping. Mechanism (working theory, not proven): batch/catch-up stream processing lands both timestamps near end of generation instead of bracketing the real thinking phase. Real cost breakdown: qwen3:8b generating at ~10-12 tok/s; prompt_eval_count constant at 2050 tokens (full context), first-in-session prompt_eval ~22.6s once then ~0.1s via Ollama's prompt cache. Disposition: confirmed upstream Open WebUI bug, unrelated to RAG/proxy/network/lab infrastructure -- out of scope to chase further without upstream access. Environment fully restored. Full detail: test-logs/Test24-log-entry.md.</t>
   </si>
 </sst>
 </file>
@@ -458,15 +485,15 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -491,13 +518,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>54430</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>43543</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>408377</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>4103914</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -836,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K35"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="18.23046875" customWidth="1"/>
@@ -1840,7 +1867,7 @@
       <c r="F31" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="11" t="s">
         <v>107</v>
       </c>
       <c r="H31" s="10" t="s">
@@ -1856,32 +1883,67 @@
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="7"/>
-    </row>
-    <row r="33" spans="2:6" ht="332.15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B33" s="11" t="s">
+    <row r="32" spans="1:11" ht="219" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A32" s="8">
+        <v>24</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="I32" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" ht="332.15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B34" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="35" spans="2:6" ht="340" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B35" s="13" t="s">
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+    </row>
+    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" spans="1:6" ht="340" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B36" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B35:F35"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/field-guide/AI_Lab_Test_Log.xlsx
+++ b/field-guide/AI_Lab_Test_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e6708a7502f50cfc/Tony1/AI-Lab/Portal/field-guide/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="43" documentId="11_82C492D49402BEC24B5B26F6D884A707973BE388" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EDA8AB4-AA6A-4DFF-B261-AABBE0915E5F}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="11_82C492D49402BEC24B5B26F6D884A707973BE388" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC09518-F31E-4C24-9A12-07F686865D19}"/>
   <bookViews>
-    <workbookView xWindow="6086" yWindow="1757" windowWidth="10371" windowHeight="7089" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6086" yWindow="1757" windowWidth="23811" windowHeight="14126" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI_Lab_Test_Log" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="128">
   <si>
     <t>Test</t>
   </si>
@@ -394,6 +394,30 @@
   </si>
   <si>
     <t>Open WebUI's on-screen 'Thought for Xs' timer showed &lt;1s on every round of a plain (non-RAG) 'why do cats purr?' query, across 10+ rounds on two separate machines (browser on Lab PC 2, then browser on the HP desktop over the network -- ruling out resource contention). Real latency agreed two independent ways: stopwatch and Ollama's own total_duration (via capture_proxy.py, same port-swap rig as Test 23) matched within 1-3s every round, 20-49s per round. Root cause confirmed from a persisted chat record (GET /api/v1/chats/{chat_id}): the same message held both the broken duration:0 (started_at/ended_at 0.19s apart, int-truncated) and Ollama's real usage.total_duration=21.80s side by side. Frontend (bundled DBZsSbCZ.js) confirmed innocent -- just renders the given duration int. Bug located in backend open_webui/utils/middleware.py (~2969-2994, duplicated ~4306-4372) timestamp stamping. Mechanism (working theory, not proven): batch/catch-up stream processing lands both timestamps near end of generation instead of bracketing the real thinking phase. Real cost breakdown: qwen3:8b generating at ~10-12 tok/s; prompt_eval_count constant at 2050 tokens (full context), first-in-session prompt_eval ~22.6s once then ~0.1s via Ollama's prompt cache. Disposition: confirmed upstream Open WebUI bug, unrelated to RAG/proxy/network/lab infrastructure -- out of scope to chase further without upstream access. Environment fully restored. Full detail: test-logs/Test24-log-entry.md.</t>
+  </si>
+  <si>
+    <t>Ollama API (direct)</t>
+  </si>
+  <si>
+    <t>Thinking on/off x output-length constraint</t>
+  </si>
+  <si>
+    <t>qwen3:8b via Ollama :11434 -- no Open WebUI, no proxy</t>
+  </si>
+  <si>
+    <t>standard prompt, unconstrained vs one-sentence-constrained, N=10/condition</t>
+  </si>
+  <si>
+    <t>n/a (measured via total_duration, not the display timer)</t>
+  </si>
+  <si>
+    <t>median total: A 89.29 / B 34.80 / C 21.54 / D 1.69</t>
+  </si>
+  <si>
+    <t>H1 and H2 confirmed -- ~53x combined</t>
+  </si>
+  <si>
+    <t>2x2 design quantifying two speed levers on qwen3:8b, measured directly against Ollama (bypassing Open WebUI entirely -- no proxy or port-swap needed since Test 24's timer bug can't contaminate a measurement that never touches Open WebUI). Conditions: A) thinking ON + unconstrained, B) thinking OFF + unconstrained, C) thinking ON + constrained, D) thinking OFF + constrained. N=10 scored trials/condition, median reported. Results: A 89.29s (1206 tok, 13.4 tok/s), B 34.80s (476 tok, 13.8 tok/s), C 21.54s (301 tok, 14.1 tok/s), D 1.69s (19 tok, 15.1 tok/s). H1 (thinking-off helps) CONFIRMED, bigger than the ~halving guess -- 61-92% reduction depending on condition; content-length check shows the visible answer stays about the same length with thinking on vs off (~2300 vs ~2110 chars), so the extra tokens with thinking on are essentially all hidden reasoning, not a longer real answer. Quality spot-check found no degradation in thinking-off answers (B stayed coherent/thorough, D correctly obeyed the one-sentence constraint every time sampled). H2 (it's token count, not rate) CONFIRMED -- tok/s held in a tight 12.8-15.1 band across all four conditions. Combined levers (A to D): ~53x faster. One honest caveat logged: condition A's median (89.29s) ran higher than the original motivating screenshot (42.88s) -- unconstrained/thinking-on answers vary a lot trial to trial (73.5-115.5s range this run), noted as expected variance, not a contradiction. Scope held to quantify-only per Tony's answer to the spec's open questions -- no persistent thinking-off config change made or proposed as an automatic follow-up. Full detail: test-logs/Test25-log-entry.md, raw trial_results.jsonl and harness script in AI-Lab-Tools/test25-response-time-bench/.</t>
   </si>
 </sst>
 </file>
@@ -1918,10 +1942,42 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="7"/>
-    </row>
-    <row r="34" spans="1:6" ht="332.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="7">
+        <v>25</v>
+      </c>
+      <c r="B33" t="s">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D33" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" t="s">
+        <v>124</v>
+      </c>
+      <c r="H33" t="s">
+        <v>125</v>
+      </c>
+      <c r="I33" t="s">
+        <v>126</v>
+      </c>
+      <c r="J33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" ht="332.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="12" t="s">
         <v>93</v>
       </c>
@@ -1930,8 +1986,8 @@
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
     </row>
-    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" spans="1:6" ht="340" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" spans="1:11" ht="340" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="14" t="s">
         <v>94</v>
       </c>

--- a/field-guide/AI_Lab_Test_Log.xlsx
+++ b/field-guide/AI_Lab_Test_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e6708a7502f50cfc/Tony1/AI-Lab/Portal/field-guide/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="11_82C492D49402BEC24B5B26F6D884A707973BE388" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BC09518-F31E-4C24-9A12-07F686865D19}"/>
+  <xr:revisionPtr revIDLastSave="43" documentId="11_82C492D49402BEC24B5B26F6D884A707973BE388" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0EDA8AB4-AA6A-4DFF-B261-AABBE0915E5F}"/>
   <bookViews>
-    <workbookView xWindow="6086" yWindow="1757" windowWidth="23811" windowHeight="14126" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6086" yWindow="1757" windowWidth="10371" windowHeight="7089" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI_Lab_Test_Log" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="120">
   <si>
     <t>Test</t>
   </si>
@@ -394,30 +394,6 @@
   </si>
   <si>
     <t>Open WebUI's on-screen 'Thought for Xs' timer showed &lt;1s on every round of a plain (non-RAG) 'why do cats purr?' query, across 10+ rounds on two separate machines (browser on Lab PC 2, then browser on the HP desktop over the network -- ruling out resource contention). Real latency agreed two independent ways: stopwatch and Ollama's own total_duration (via capture_proxy.py, same port-swap rig as Test 23) matched within 1-3s every round, 20-49s per round. Root cause confirmed from a persisted chat record (GET /api/v1/chats/{chat_id}): the same message held both the broken duration:0 (started_at/ended_at 0.19s apart, int-truncated) and Ollama's real usage.total_duration=21.80s side by side. Frontend (bundled DBZsSbCZ.js) confirmed innocent -- just renders the given duration int. Bug located in backend open_webui/utils/middleware.py (~2969-2994, duplicated ~4306-4372) timestamp stamping. Mechanism (working theory, not proven): batch/catch-up stream processing lands both timestamps near end of generation instead of bracketing the real thinking phase. Real cost breakdown: qwen3:8b generating at ~10-12 tok/s; prompt_eval_count constant at 2050 tokens (full context), first-in-session prompt_eval ~22.6s once then ~0.1s via Ollama's prompt cache. Disposition: confirmed upstream Open WebUI bug, unrelated to RAG/proxy/network/lab infrastructure -- out of scope to chase further without upstream access. Environment fully restored. Full detail: test-logs/Test24-log-entry.md.</t>
-  </si>
-  <si>
-    <t>Ollama API (direct)</t>
-  </si>
-  <si>
-    <t>Thinking on/off x output-length constraint</t>
-  </si>
-  <si>
-    <t>qwen3:8b via Ollama :11434 -- no Open WebUI, no proxy</t>
-  </si>
-  <si>
-    <t>standard prompt, unconstrained vs one-sentence-constrained, N=10/condition</t>
-  </si>
-  <si>
-    <t>n/a (measured via total_duration, not the display timer)</t>
-  </si>
-  <si>
-    <t>median total: A 89.29 / B 34.80 / C 21.54 / D 1.69</t>
-  </si>
-  <si>
-    <t>H1 and H2 confirmed -- ~53x combined</t>
-  </si>
-  <si>
-    <t>2x2 design quantifying two speed levers on qwen3:8b, measured directly against Ollama (bypassing Open WebUI entirely -- no proxy or port-swap needed since Test 24's timer bug can't contaminate a measurement that never touches Open WebUI). Conditions: A) thinking ON + unconstrained, B) thinking OFF + unconstrained, C) thinking ON + constrained, D) thinking OFF + constrained. N=10 scored trials/condition, median reported. Results: A 89.29s (1206 tok, 13.4 tok/s), B 34.80s (476 tok, 13.8 tok/s), C 21.54s (301 tok, 14.1 tok/s), D 1.69s (19 tok, 15.1 tok/s). H1 (thinking-off helps) CONFIRMED, bigger than the ~halving guess -- 61-92% reduction depending on condition; content-length check shows the visible answer stays about the same length with thinking on vs off (~2300 vs ~2110 chars), so the extra tokens with thinking on are essentially all hidden reasoning, not a longer real answer. Quality spot-check found no degradation in thinking-off answers (B stayed coherent/thorough, D correctly obeyed the one-sentence constraint every time sampled). H2 (it's token count, not rate) CONFIRMED -- tok/s held in a tight 12.8-15.1 band across all four conditions. Combined levers (A to D): ~53x faster. One honest caveat logged: condition A's median (89.29s) ran higher than the original motivating screenshot (42.88s) -- unconstrained/thinking-on answers vary a lot trial to trial (73.5-115.5s range this run), noted as expected variance, not a contradiction. Scope held to quantify-only per Tony's answer to the spec's open questions -- no persistent thinking-off config change made or proposed as an automatic follow-up. Full detail: test-logs/Test25-log-entry.md, raw trial_results.jsonl and harness script in AI-Lab-Tools/test25-response-time-bench/.</t>
   </si>
 </sst>
 </file>
@@ -1942,42 +1918,10 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="7">
-        <v>25</v>
-      </c>
-      <c r="B33" t="s">
-        <v>29</v>
-      </c>
-      <c r="C33" t="s">
-        <v>120</v>
-      </c>
-      <c r="D33" t="s">
-        <v>121</v>
-      </c>
-      <c r="E33" t="s">
-        <v>122</v>
-      </c>
-      <c r="F33" t="s">
-        <v>123</v>
-      </c>
-      <c r="G33" t="s">
-        <v>124</v>
-      </c>
-      <c r="H33" t="s">
-        <v>125</v>
-      </c>
-      <c r="I33" t="s">
-        <v>126</v>
-      </c>
-      <c r="J33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" ht="332.15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" ht="332.15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B34" s="12" t="s">
         <v>93</v>
       </c>
@@ -1986,8 +1930,8 @@
       <c r="E34" s="13"/>
       <c r="F34" s="13"/>
     </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="36" spans="1:11" ht="340" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="36" spans="1:6" ht="340" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B36" s="14" t="s">
         <v>94</v>
       </c>
